--- a/crates/xlstream-eval/tests/fixtures/lookup/hlookup.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/lookup/hlookup.xlsx
@@ -21,9 +21,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t xml:space="preserve">hlookup</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="7">
+  <si>
+    <t xml:space="preserve">quarter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hlookup_row2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hlookup_row3</t>
   </si>
   <si>
     <t xml:space="preserve">Q1</t>
@@ -308,18 +314,96 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <f aca="false">HLOOKUP("Q2",HLookup!A1:D3,2,FALSE())</f>
+      <c r="A2" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <f aca="false">HLOOKUP(A2,HLookup!A1:D3,2,FALSE())</f>
+        <v>100</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <f aca="false">HLOOKUP(A2,HLookup!A1:D3,3,FALSE())</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <f aca="false">HLOOKUP(A3,HLookup!A1:D3,2,FALSE())</f>
         <v>200</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <f aca="false">HLOOKUP(A3,HLookup!A1:D3,3,FALSE())</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <f aca="false">HLOOKUP(A4,HLookup!A1:D3,2,FALSE())</f>
+        <v>300</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <f aca="false">HLOOKUP(A4,HLookup!A1:D3,3,FALSE())</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <f aca="false">HLOOKUP(A5,HLookup!A1:D3,2,FALSE())</f>
+        <v>400</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <f aca="false">HLOOKUP(A5,HLookup!A1:D3,3,FALSE())</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <f aca="false">HLOOKUP(A6,HLookup!A1:D3,2,FALSE())</f>
+        <v>100</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <f aca="false">HLOOKUP(A6,HLookup!A1:D3,3,FALSE())</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <f aca="false">HLOOKUP(A7,HLookup!A1:D3,2,FALSE())</f>
+        <v>300</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <f aca="false">HLOOKUP(A7,HLookup!A1:D3,3,FALSE())</f>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -343,16 +427,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
